--- a/2022 data/excel_outputs/201_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/201_boothwise_data.xlsx
@@ -14,11 +14,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="548">
   <si>
     <t>AC 201 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -235,7 +298,7 @@
     <t>U.P.V. KARWA KHURD ( COMPOSITE 1-8) ROOM-2</t>
   </si>
   <si>
-    <t>U.P.V. MANGUPUR ( COMPOSITE 1-8) ■■■■-1</t>
+    <t>AIITAP AIIMDAMT SHRANADAPAVAT BHPAHI AIBIVAVAS KIMACHANATAM CHMAAM JMS</t>
   </si>
   <si>
     <t>U.P.V. MANGUPUR ( COMPOSITE 1-8) ROOM-2</t>
@@ -1601,8 +1664,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1618,7 +1689,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1626,12 +1697,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1930,76 +2019,139 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="D2" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="E2" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="F2" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="G2" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="H2" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="I2" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="J2" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="K2" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="L2" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="M2" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="N2" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="O2" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="P2" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="Q2" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="R2" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="S2" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="T2" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="U2" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="V2" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -2007,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>1011</v>
@@ -2075,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>718</v>
@@ -2143,7 +2295,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>1094</v>
@@ -2211,7 +2363,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>760</v>
@@ -2279,7 +2431,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>1098</v>
@@ -2347,7 +2499,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>443</v>
@@ -2415,7 +2567,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>1052</v>
@@ -2483,7 +2635,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>1036</v>
@@ -2551,7 +2703,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>888</v>
@@ -2619,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>787</v>
@@ -2687,7 +2839,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>880</v>
@@ -2755,7 +2907,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>438</v>
@@ -2823,7 +2975,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>1165</v>
@@ -2891,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>960</v>
@@ -2959,7 +3111,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>857</v>
@@ -3027,7 +3179,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>879</v>
@@ -3095,7 +3247,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>728</v>
@@ -3163,7 +3315,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>1082</v>
@@ -3231,7 +3383,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>956</v>
@@ -3299,7 +3451,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>568</v>
@@ -3367,7 +3519,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>1114</v>
@@ -3435,7 +3587,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>1020</v>
@@ -3503,7 +3655,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>1092</v>
@@ -3571,7 +3723,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>1032</v>
@@ -3639,7 +3791,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>1132</v>
@@ -3707,7 +3859,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1198</v>
@@ -3775,7 +3927,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>1029</v>
@@ -3843,7 +3995,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1199</v>
@@ -3911,7 +4063,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1066</v>
@@ -3979,7 +4131,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1075</v>
@@ -4047,7 +4199,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>876</v>
@@ -4115,7 +4267,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>911</v>
@@ -4183,7 +4335,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>989</v>
@@ -4251,7 +4403,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>977</v>
@@ -4319,7 +4471,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>928</v>
@@ -4387,7 +4539,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>936</v>
@@ -4455,7 +4607,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C39">
         <v>781</v>
@@ -4523,7 +4675,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>619</v>
@@ -4591,7 +4743,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>633</v>
@@ -4659,7 +4811,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>765</v>
@@ -4727,7 +4879,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <v>724</v>
@@ -4795,7 +4947,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C44">
         <v>766</v>
@@ -4863,7 +5015,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C45">
         <v>1074</v>
@@ -4931,7 +5083,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C46">
         <v>1087</v>
@@ -4999,7 +5151,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <v>698</v>
@@ -5067,7 +5219,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <v>1047</v>
@@ -5135,7 +5287,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <v>702</v>
@@ -5203,7 +5355,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C50">
         <v>1096</v>
@@ -5271,7 +5423,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C51">
         <v>1123</v>
@@ -5339,7 +5491,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C52">
         <v>1002</v>
@@ -5407,7 +5559,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <v>812</v>
@@ -5475,7 +5627,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C54">
         <v>873</v>
@@ -5543,7 +5695,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <v>527</v>
@@ -5611,7 +5763,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <v>331</v>
@@ -5679,7 +5831,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C57">
         <v>616</v>
@@ -5747,7 +5899,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C58">
         <v>659</v>
@@ -5815,7 +5967,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C59">
         <v>627</v>
@@ -5883,7 +6035,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>583</v>
@@ -5951,7 +6103,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C61">
         <v>1013</v>
@@ -6019,7 +6171,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C62">
         <v>668</v>
@@ -6087,7 +6239,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C63">
         <v>738</v>
@@ -6155,7 +6307,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C64">
         <v>559</v>
@@ -6223,7 +6375,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C65">
         <v>880</v>
@@ -6291,7 +6443,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C66">
         <v>802</v>
@@ -6359,7 +6511,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C67">
         <v>640</v>
@@ -6427,7 +6579,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C68">
         <v>852</v>
@@ -6495,7 +6647,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C69">
         <v>967</v>
@@ -6563,7 +6715,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C70">
         <v>921</v>
@@ -6631,7 +6783,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C71">
         <v>1102</v>
@@ -6699,7 +6851,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C72">
         <v>894</v>
@@ -6767,7 +6919,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C73">
         <v>948</v>
@@ -6835,7 +6987,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C74">
         <v>1010</v>
@@ -6903,7 +7055,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C75">
         <v>1009</v>
@@ -6971,7 +7123,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C76">
         <v>586</v>
@@ -7039,7 +7191,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>803</v>
@@ -7107,7 +7259,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>1064</v>
@@ -7175,7 +7327,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C79">
         <v>667</v>
@@ -7243,7 +7395,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C80">
         <v>1176</v>
@@ -7311,7 +7463,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C81">
         <v>899</v>
@@ -7379,7 +7531,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C82">
         <v>951</v>
@@ -7447,7 +7599,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C83">
         <v>785</v>
@@ -7515,7 +7667,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>795</v>
@@ -7583,7 +7735,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C85">
         <v>866</v>
@@ -7651,7 +7803,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C86">
         <v>774</v>
@@ -7719,7 +7871,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C87">
         <v>985</v>
@@ -7787,7 +7939,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C88">
         <v>456</v>
@@ -7855,7 +8007,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C89">
         <v>1134</v>
@@ -7923,7 +8075,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C90">
         <v>1148</v>
@@ -7991,7 +8143,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C91">
         <v>1171</v>
@@ -8059,7 +8211,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C92">
         <v>961</v>
@@ -8127,7 +8279,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C93">
         <v>610</v>
@@ -8195,7 +8347,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C94">
         <v>368</v>
@@ -8263,7 +8415,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C95">
         <v>609</v>
@@ -8331,7 +8483,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C96">
         <v>930</v>
@@ -8399,7 +8551,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C97">
         <v>1134</v>
@@ -8467,7 +8619,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C98">
         <v>1172</v>
@@ -8535,7 +8687,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C99">
         <v>1006</v>
@@ -8603,7 +8755,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C100">
         <v>1089</v>
@@ -8671,7 +8823,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C101">
         <v>864</v>
@@ -8739,7 +8891,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C102">
         <v>857</v>
@@ -8807,7 +8959,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C103">
         <v>781</v>
@@ -8875,7 +9027,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C104">
         <v>498</v>
@@ -8943,7 +9095,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C105">
         <v>558</v>
@@ -9011,7 +9163,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C106">
         <v>961</v>
@@ -9079,7 +9231,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C107">
         <v>596</v>
@@ -9147,7 +9299,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C108">
         <v>1079</v>
@@ -9215,7 +9367,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C109">
         <v>637</v>
@@ -9283,7 +9435,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C110">
         <v>690</v>
@@ -9351,7 +9503,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C111">
         <v>624</v>
@@ -9419,7 +9571,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C112">
         <v>903</v>
@@ -9487,7 +9639,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C113">
         <v>576</v>
@@ -9555,7 +9707,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C114">
         <v>704</v>
@@ -9623,7 +9775,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C115">
         <v>818</v>
@@ -9691,7 +9843,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="C116">
         <v>1005</v>
@@ -9759,7 +9911,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C117">
         <v>1162</v>
@@ -9827,7 +9979,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C118">
         <v>674</v>
@@ -9895,7 +10047,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C119">
         <v>705</v>
@@ -9963,7 +10115,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C120">
         <v>619</v>
@@ -10031,7 +10183,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C121">
         <v>627</v>
@@ -10099,7 +10251,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C122">
         <v>827</v>
@@ -10167,7 +10319,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C123">
         <v>800</v>
@@ -10235,7 +10387,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C124">
         <v>533</v>
@@ -10303,7 +10455,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C125">
         <v>762</v>
@@ -10371,7 +10523,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C126">
         <v>1156</v>
@@ -10439,7 +10591,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C127">
         <v>614</v>
@@ -10507,7 +10659,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C128">
         <v>1106</v>
@@ -10575,7 +10727,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C129">
         <v>1136</v>
@@ -10643,7 +10795,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C130">
         <v>963</v>
@@ -10711,7 +10863,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C131">
         <v>536</v>
@@ -10779,7 +10931,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C132">
         <v>751</v>
@@ -10847,7 +10999,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C133">
         <v>612</v>
@@ -10915,7 +11067,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C134">
         <v>824</v>
@@ -10983,7 +11135,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C135">
         <v>579</v>
@@ -11051,7 +11203,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C136">
         <v>681</v>
@@ -11119,7 +11271,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C137">
         <v>740</v>
@@ -11187,7 +11339,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C138">
         <v>1000</v>
@@ -11255,7 +11407,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C139">
         <v>312</v>
@@ -11323,7 +11475,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C140">
         <v>753</v>
@@ -11391,7 +11543,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C141">
         <v>661</v>
@@ -11459,7 +11611,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C142">
         <v>907</v>
@@ -11527,7 +11679,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C143">
         <v>1094</v>
@@ -11595,7 +11747,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="C144">
         <v>808</v>
@@ -11663,7 +11815,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C145">
         <v>664</v>
@@ -11731,7 +11883,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C146">
         <v>966</v>
@@ -11799,7 +11951,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C147">
         <v>726</v>
@@ -11867,7 +12019,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>540</v>
@@ -11935,7 +12087,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>1195</v>
@@ -12003,7 +12155,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>526</v>
@@ -12071,7 +12223,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C151">
         <v>560</v>
@@ -12139,7 +12291,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>623</v>
@@ -12207,7 +12359,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C153">
         <v>645</v>
@@ -12275,7 +12427,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C154">
         <v>807</v>
@@ -12343,7 +12495,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>725</v>
@@ -12411,7 +12563,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C156">
         <v>361</v>
@@ -12479,7 +12631,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C157">
         <v>1147</v>
@@ -12547,7 +12699,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C158">
         <v>821</v>
@@ -12615,7 +12767,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C159">
         <v>1180</v>
@@ -12683,7 +12835,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C160">
         <v>1055</v>
@@ -12751,7 +12903,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C161">
         <v>939</v>
@@ -12819,7 +12971,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C162">
         <v>960</v>
@@ -12887,7 +13039,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C163">
         <v>951</v>
@@ -12955,7 +13107,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C164">
         <v>777</v>
@@ -13023,7 +13175,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>391</v>
@@ -13091,7 +13243,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C166">
         <v>758</v>
@@ -13159,7 +13311,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C167">
         <v>786</v>
@@ -13227,7 +13379,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="C168">
         <v>599</v>
@@ -13295,7 +13447,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C169">
         <v>618</v>
@@ -13363,7 +13515,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="C170">
         <v>495</v>
@@ -13431,7 +13583,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C171">
         <v>921</v>
@@ -13499,7 +13651,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="C172">
         <v>518</v>
@@ -13567,7 +13719,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C173">
         <v>964</v>
@@ -13635,7 +13787,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C174">
         <v>813</v>
@@ -13703,7 +13855,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C175">
         <v>996</v>
@@ -13771,7 +13923,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C176">
         <v>914</v>
@@ -13839,7 +13991,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C177">
         <v>1085</v>
@@ -13907,7 +14059,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C178">
         <v>987</v>
@@ -13975,7 +14127,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C179">
         <v>976</v>
@@ -14043,7 +14195,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C180">
         <v>552</v>
@@ -14111,7 +14263,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="C181">
         <v>723</v>
@@ -14179,7 +14331,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C182">
         <v>509</v>
@@ -14247,7 +14399,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C183">
         <v>765</v>
@@ -14315,7 +14467,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C184">
         <v>1136</v>
@@ -14383,7 +14535,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C185">
         <v>678</v>
@@ -14451,7 +14603,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C186">
         <v>1095</v>
@@ -14519,7 +14671,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C187">
         <v>902</v>
@@ -14587,7 +14739,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C188">
         <v>1052</v>
@@ -14655,7 +14807,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C189">
         <v>815</v>
@@ -14723,7 +14875,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C190">
         <v>626</v>
@@ -14791,7 +14943,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C191">
         <v>720</v>
@@ -14859,7 +15011,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C192">
         <v>537</v>
@@ -14927,7 +15079,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C193">
         <v>671</v>
@@ -14995,7 +15147,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C194">
         <v>732</v>
@@ -15063,7 +15215,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C195">
         <v>786</v>
@@ -15131,7 +15283,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C196">
         <v>975</v>
@@ -15199,7 +15351,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C197">
         <v>867</v>
@@ -15267,7 +15419,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C198">
         <v>939</v>
@@ -15335,7 +15487,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C199">
         <v>386</v>
@@ -15403,7 +15555,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C200">
         <v>803</v>
@@ -15471,7 +15623,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C201">
         <v>405</v>
@@ -15539,7 +15691,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C202">
         <v>621</v>
@@ -15607,7 +15759,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C203">
         <v>651</v>
@@ -15675,7 +15827,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C204">
         <v>1037</v>
@@ -15743,7 +15895,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C205">
         <v>620</v>
@@ -15811,7 +15963,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C206">
         <v>623</v>
@@ -15879,7 +16031,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C207">
         <v>821</v>
@@ -15947,7 +16099,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C208">
         <v>676</v>
@@ -16015,7 +16167,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C209">
         <v>611</v>
@@ -16083,7 +16235,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C210">
         <v>886</v>
@@ -16151,7 +16303,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C211">
         <v>1001</v>
@@ -16219,7 +16371,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C212">
         <v>1092</v>
@@ -16287,7 +16439,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C213">
         <v>1056</v>
@@ -16355,7 +16507,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C214">
         <v>999</v>
@@ -16423,7 +16575,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="C215">
         <v>847</v>
@@ -16491,7 +16643,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="C216">
         <v>939</v>
@@ -16559,7 +16711,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C217">
         <v>914</v>
@@ -16627,7 +16779,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="C218">
         <v>1093</v>
@@ -16695,7 +16847,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="C219">
         <v>1028</v>
@@ -16763,7 +16915,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C220">
         <v>726</v>
@@ -16831,7 +16983,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C221">
         <v>767</v>
@@ -16899,7 +17051,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C222">
         <v>1059</v>
@@ -16967,7 +17119,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C223">
         <v>1116</v>
@@ -17035,7 +17187,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="C224">
         <v>643</v>
@@ -17103,7 +17255,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="C225">
         <v>451</v>
@@ -17171,7 +17323,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C226">
         <v>993</v>
@@ -17239,7 +17391,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C227">
         <v>602</v>
@@ -17307,7 +17459,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C228">
         <v>806</v>
@@ -17375,7 +17527,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C229">
         <v>918</v>
@@ -17443,7 +17595,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="C230">
         <v>778</v>
@@ -17511,7 +17663,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="C231">
         <v>352</v>
@@ -17579,7 +17731,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C232">
         <v>644</v>
@@ -17647,7 +17799,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C233">
         <v>1051</v>
@@ -17715,7 +17867,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="C234">
         <v>563</v>
@@ -17783,7 +17935,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C235">
         <v>803</v>
@@ -17851,7 +18003,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="C236">
         <v>971</v>
@@ -17919,7 +18071,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>768</v>
@@ -17987,7 +18139,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C238">
         <v>1029</v>
@@ -18055,7 +18207,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>841</v>
@@ -18123,7 +18275,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C240">
         <v>680</v>
@@ -18191,7 +18343,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="C241">
         <v>677</v>
@@ -18259,7 +18411,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C242">
         <v>1002</v>
@@ -18327,7 +18479,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C243">
         <v>866</v>
@@ -18395,7 +18547,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C244">
         <v>637</v>
@@ -18463,7 +18615,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C245">
         <v>921</v>
@@ -18531,7 +18683,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C246">
         <v>659</v>
@@ -18599,7 +18751,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C247">
         <v>1196</v>
@@ -18667,7 +18819,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C248">
         <v>1098</v>
@@ -18735,7 +18887,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C249">
         <v>724</v>
@@ -18803,7 +18955,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C250">
         <v>715</v>
@@ -18871,7 +19023,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C251">
         <v>687</v>
@@ -18939,7 +19091,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C252">
         <v>1129</v>
@@ -19007,7 +19159,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C253">
         <v>560</v>
@@ -19075,7 +19227,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="C254">
         <v>896</v>
@@ -19143,7 +19295,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C255">
         <v>960</v>
@@ -19211,7 +19363,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="C256">
         <v>899</v>
@@ -19279,7 +19431,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="C257">
         <v>1031</v>
@@ -19347,7 +19499,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C258">
         <v>482</v>
@@ -19415,7 +19567,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C259">
         <v>669</v>
@@ -19483,7 +19635,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="C260">
         <v>861</v>
@@ -19551,7 +19703,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C261">
         <v>688</v>
@@ -19619,7 +19771,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C262">
         <v>972</v>
@@ -19687,7 +19839,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C263">
         <v>947</v>
@@ -19755,7 +19907,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="C264">
         <v>1105</v>
@@ -19823,7 +19975,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="C265">
         <v>1099</v>
@@ -19891,7 +20043,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C266">
         <v>711</v>
@@ -19959,7 +20111,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="C267">
         <v>662</v>
@@ -20027,7 +20179,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C268">
         <v>301</v>
@@ -20095,7 +20247,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="C269">
         <v>746</v>
@@ -20163,7 +20315,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C270">
         <v>663</v>
@@ -20231,7 +20383,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C271">
         <v>873</v>
@@ -20299,7 +20451,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C272">
         <v>856</v>
@@ -20367,7 +20519,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C273">
         <v>816</v>
@@ -20435,7 +20587,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C274">
         <v>890</v>
@@ -20503,7 +20655,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C275">
         <v>992</v>
@@ -20571,7 +20723,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C276">
         <v>1039</v>
@@ -20639,7 +20791,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C277">
         <v>1123</v>
@@ -20707,7 +20859,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C278">
         <v>768</v>
@@ -20775,7 +20927,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C279">
         <v>806</v>
@@ -20843,7 +20995,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C280">
         <v>1022</v>
@@ -20911,7 +21063,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="C281">
         <v>1119</v>
@@ -20979,7 +21131,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C282">
         <v>1043</v>
@@ -21047,7 +21199,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="C283">
         <v>1127</v>
@@ -21115,7 +21267,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="C284">
         <v>707</v>
@@ -21183,7 +21335,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="C285">
         <v>707</v>
@@ -21251,7 +21403,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C286">
         <v>962</v>
@@ -21319,7 +21471,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="C287">
         <v>1021</v>
@@ -21387,7 +21539,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C288">
         <v>815</v>
@@ -21455,7 +21607,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C289">
         <v>803</v>
@@ -21523,7 +21675,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C290">
         <v>1005</v>
@@ -21591,7 +21743,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C291">
         <v>998</v>
@@ -21659,7 +21811,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C292">
         <v>716</v>
@@ -21727,7 +21879,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C293">
         <v>480</v>
@@ -21795,7 +21947,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C294">
         <v>905</v>
@@ -21863,7 +22015,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C295">
         <v>1155</v>
@@ -21931,7 +22083,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C296">
         <v>1159</v>
@@ -21999,7 +22151,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C297">
         <v>1159</v>
@@ -22067,7 +22219,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C298">
         <v>1097</v>
@@ -22135,7 +22287,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C299">
         <v>287</v>
@@ -22203,7 +22355,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C300">
         <v>1200</v>
@@ -22271,7 +22423,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C301">
         <v>1159</v>
@@ -22339,7 +22491,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C302">
         <v>700</v>
@@ -22407,7 +22559,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C303">
         <v>869</v>
@@ -22475,7 +22627,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C304">
         <v>413</v>
@@ -22543,7 +22695,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C305">
         <v>1149</v>
@@ -22611,7 +22763,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C306">
         <v>1172</v>
@@ -22679,7 +22831,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C307">
         <v>500</v>
@@ -22747,7 +22899,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C308">
         <v>803</v>
@@ -22815,7 +22967,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C309">
         <v>907</v>
@@ -22883,7 +23035,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C310">
         <v>733</v>
@@ -22951,7 +23103,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C311">
         <v>855</v>
@@ -23019,7 +23171,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C312">
         <v>1206</v>
@@ -23087,7 +23239,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C313">
         <v>901</v>
@@ -23155,7 +23307,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C314">
         <v>1156</v>
@@ -23223,7 +23375,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C315">
         <v>1034</v>
@@ -23291,7 +23443,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="C316">
         <v>1117</v>
@@ -23359,7 +23511,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C317">
         <v>860</v>
@@ -23427,7 +23579,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C318">
         <v>408</v>
@@ -23495,7 +23647,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C319">
         <v>865</v>
@@ -23563,7 +23715,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C320">
         <v>966</v>
@@ -23631,7 +23783,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="C321">
         <v>521</v>
@@ -23699,7 +23851,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="C322">
         <v>825</v>
@@ -23767,7 +23919,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C323">
         <v>961</v>
@@ -23835,7 +23987,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="C324">
         <v>578</v>
@@ -23903,7 +24055,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="C325">
         <v>734</v>
@@ -23971,7 +24123,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C326">
         <v>1004</v>
@@ -24039,7 +24191,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="C327">
         <v>842</v>
@@ -24107,7 +24259,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="C328">
         <v>963</v>
@@ -24175,7 +24327,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C329">
         <v>1031</v>
@@ -24243,7 +24395,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C330">
         <v>819</v>
@@ -24311,7 +24463,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C331">
         <v>656</v>
@@ -24379,7 +24531,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="C332">
         <v>654</v>
@@ -24447,7 +24599,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="C333">
         <v>924</v>
@@ -24515,7 +24667,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="C334">
         <v>1110</v>
@@ -24583,7 +24735,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C335">
         <v>892</v>
@@ -24651,7 +24803,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="C336">
         <v>1120</v>
@@ -24719,7 +24871,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="C337">
         <v>722</v>
@@ -24787,7 +24939,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="C338">
         <v>759</v>
@@ -24855,7 +25007,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C339">
         <v>768</v>
@@ -24923,7 +25075,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C340">
         <v>632</v>
@@ -24991,7 +25143,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="C341">
         <v>926</v>
@@ -25059,7 +25211,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="C342">
         <v>546</v>
@@ -25127,7 +25279,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C343">
         <v>710</v>
@@ -25195,7 +25347,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C344">
         <v>866</v>
@@ -25263,7 +25415,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="C345">
         <v>892</v>
@@ -25331,7 +25483,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C346">
         <v>927</v>
@@ -25399,7 +25551,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C347">
         <v>850</v>
@@ -25467,7 +25619,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C348">
         <v>591</v>
@@ -25535,7 +25687,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="C349">
         <v>422</v>
@@ -25603,7 +25755,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C350">
         <v>1051</v>
@@ -25671,7 +25823,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C351">
         <v>955</v>
@@ -25739,7 +25891,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="C352">
         <v>902</v>
@@ -25807,7 +25959,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C353">
         <v>1088</v>
@@ -25875,7 +26027,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C354">
         <v>939</v>
@@ -25943,7 +26095,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="C355">
         <v>1017</v>
@@ -26011,7 +26163,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C356">
         <v>748</v>
@@ -26079,7 +26231,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="C357">
         <v>1002</v>
@@ -26147,7 +26299,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C358">
         <v>806</v>
@@ -26215,7 +26367,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C359">
         <v>505</v>
@@ -26283,7 +26435,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C360">
         <v>787</v>
@@ -26351,7 +26503,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C361">
         <v>698</v>
@@ -26419,7 +26571,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C362">
         <v>785</v>
@@ -26487,7 +26639,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C363">
         <v>758</v>
@@ -26555,7 +26707,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="C364">
         <v>695</v>
@@ -26623,7 +26775,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C365">
         <v>491</v>
@@ -26691,7 +26843,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="C366">
         <v>633</v>
@@ -26759,7 +26911,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="C367">
         <v>967</v>
@@ -26827,7 +26979,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C368">
         <v>927</v>
@@ -26895,7 +27047,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="C369">
         <v>689</v>
@@ -26963,7 +27115,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="C370">
         <v>666</v>
@@ -27031,7 +27183,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C371">
         <v>688</v>
@@ -27099,7 +27251,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C372">
         <v>1051</v>
@@ -27167,7 +27319,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C373">
         <v>1019</v>
@@ -27235,7 +27387,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="C374">
         <v>977</v>
@@ -27303,7 +27455,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C375">
         <v>823</v>
@@ -27371,7 +27523,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="C376">
         <v>1081</v>
@@ -27439,7 +27591,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C377">
         <v>411</v>
@@ -27507,7 +27659,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C378">
         <v>745</v>
@@ -27575,7 +27727,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C379">
         <v>1061</v>
@@ -27643,7 +27795,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="C380">
         <v>843</v>
@@ -27711,7 +27863,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C381">
         <v>776</v>
@@ -27779,7 +27931,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="C382">
         <v>1028</v>
@@ -27847,7 +27999,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="C383">
         <v>614</v>
@@ -27915,7 +28067,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C384">
         <v>701</v>
@@ -27983,7 +28135,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="C385">
         <v>903</v>
@@ -28051,7 +28203,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C386">
         <v>631</v>
@@ -28119,7 +28271,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="C387">
         <v>748</v>
@@ -28187,7 +28339,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C388">
         <v>536</v>
@@ -28255,7 +28407,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="C389">
         <v>374</v>
@@ -28323,7 +28475,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="C390">
         <v>854</v>
@@ -28391,7 +28543,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C391">
         <v>1159</v>
@@ -28459,7 +28611,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C392">
         <v>451</v>
@@ -28527,7 +28679,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C393">
         <v>694</v>
@@ -28595,7 +28747,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C394">
         <v>665</v>
@@ -28663,7 +28815,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="C395">
         <v>929</v>
@@ -28731,7 +28883,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="C396">
         <v>1042</v>
@@ -28799,7 +28951,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C397">
         <v>624</v>
@@ -28867,7 +29019,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="C398">
         <v>637</v>
@@ -28935,7 +29087,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C399">
         <v>546</v>
@@ -29003,7 +29155,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C400">
         <v>515</v>
@@ -29071,7 +29223,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="C401">
         <v>463</v>
@@ -29139,7 +29291,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="C402">
         <v>423</v>
@@ -29207,7 +29359,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C403">
         <v>1018</v>
@@ -29275,7 +29427,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="C404">
         <v>797</v>
@@ -29343,7 +29495,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="C405">
         <v>1042</v>
@@ -29411,7 +29563,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="C406">
         <v>487</v>
@@ -29479,7 +29631,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="C407">
         <v>897</v>
@@ -29547,7 +29699,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C408">
         <v>809</v>
@@ -29615,7 +29767,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C409">
         <v>642</v>
@@ -29683,7 +29835,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C410">
         <v>850</v>
@@ -29751,7 +29903,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="C411">
         <v>1155</v>
@@ -29819,7 +29971,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="C412">
         <v>823</v>
@@ -29887,7 +30039,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="C413">
         <v>1050</v>
@@ -29955,7 +30107,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C414">
         <v>691</v>
@@ -30023,7 +30175,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="C415">
         <v>554</v>
@@ -30091,7 +30243,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="C416">
         <v>596</v>
@@ -30159,7 +30311,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="C417">
         <v>837</v>
@@ -30227,7 +30379,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C418">
         <v>709</v>
@@ -30295,7 +30447,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="C419">
         <v>883</v>
@@ -30363,7 +30515,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="C420">
         <v>336</v>
@@ -30431,7 +30583,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C421">
         <v>784</v>
@@ -30499,7 +30651,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C422">
         <v>759</v>
@@ -30567,7 +30719,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="C423">
         <v>844</v>
@@ -30635,7 +30787,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="C424">
         <v>728</v>
@@ -30703,7 +30855,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C425">
         <v>457</v>
@@ -30771,7 +30923,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C426">
         <v>603</v>
@@ -30839,7 +30991,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="C427">
         <v>679</v>
@@ -30907,7 +31059,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C428">
         <v>567</v>
@@ -30975,7 +31127,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="C429">
         <v>607</v>
@@ -31043,7 +31195,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C430">
         <v>586</v>
@@ -31111,7 +31263,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C431">
         <v>830</v>
@@ -31179,7 +31331,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="C432">
         <v>1078</v>
@@ -31247,7 +31399,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C433">
         <v>599</v>
@@ -31315,7 +31467,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="C434">
         <v>369</v>
@@ -31383,7 +31535,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C435">
         <v>621</v>
@@ -31451,7 +31603,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="C436">
         <v>731</v>
@@ -31519,7 +31671,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="C437">
         <v>1023</v>
@@ -31587,7 +31739,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C438">
         <v>387</v>
@@ -31655,7 +31807,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="C439">
         <v>715</v>
@@ -31723,7 +31875,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="C440">
         <v>629</v>
@@ -31791,7 +31943,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C441">
         <v>647</v>
@@ -31859,7 +32011,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="C442">
         <v>617</v>
@@ -31927,7 +32079,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="C443">
         <v>666</v>
@@ -31995,7 +32147,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="C444">
         <v>401</v>
@@ -32063,7 +32215,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="C445">
         <v>873</v>
@@ -32131,7 +32283,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="C446">
         <v>667</v>
@@ -32199,7 +32351,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="C447">
         <v>431</v>
@@ -32267,7 +32419,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="C448">
         <v>784</v>
@@ -32335,7 +32487,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="C449">
         <v>519</v>
@@ -32403,7 +32555,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="C450">
         <v>451</v>
@@ -32471,7 +32623,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="C451">
         <v>444</v>
@@ -32539,7 +32691,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="C452">
         <v>650</v>
@@ -32607,7 +32759,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="C453">
         <v>938</v>
@@ -32675,7 +32827,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="C454">
         <v>665</v>
@@ -32743,7 +32895,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="C455">
         <v>668</v>
@@ -32811,7 +32963,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="C456">
         <v>608</v>
@@ -32879,7 +33031,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="C457">
         <v>455</v>
@@ -32947,7 +33099,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="C458">
         <v>910</v>
@@ -33015,7 +33167,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="C459">
         <v>812</v>
@@ -33083,7 +33235,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="C460">
         <v>230</v>
@@ -33151,7 +33303,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="C461">
         <v>654</v>
@@ -33219,7 +33371,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="C462">
         <v>570</v>
@@ -33287,7 +33439,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="C463">
         <v>725</v>
@@ -33355,7 +33507,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="C464">
         <v>573</v>
@@ -33423,7 +33575,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="C465">
         <v>647</v>
@@ -33491,7 +33643,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C466">
         <v>516</v>
@@ -33559,7 +33711,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="C467">
         <v>580</v>
@@ -33627,7 +33779,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C468">
         <v>612</v>
@@ -33695,7 +33847,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C469">
         <v>402</v>
@@ -33763,7 +33915,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="C470">
         <v>1110</v>
@@ -33831,7 +33983,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="C471">
         <v>917</v>
@@ -33899,7 +34051,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="C472">
         <v>523</v>
@@ -33967,7 +34119,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="C473">
         <v>601</v>
@@ -34035,7 +34187,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="C474">
         <v>574</v>
@@ -34103,7 +34255,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="C475">
         <v>1104</v>
@@ -34171,7 +34323,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="C476">
         <v>649</v>
@@ -34239,7 +34391,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="C477">
         <v>633</v>
@@ -34307,7 +34459,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="C478">
         <v>501</v>
@@ -34375,7 +34527,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="C479">
         <v>519</v>
@@ -34443,7 +34595,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="C480">
         <v>468</v>
@@ -34511,7 +34663,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="C481">
         <v>264</v>
@@ -34579,7 +34731,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="C482">
         <v>396</v>
@@ -34647,7 +34799,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="C483">
         <v>992</v>
@@ -34715,7 +34867,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="C484">
         <v>836</v>
@@ -34783,7 +34935,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="C485">
         <v>981</v>
@@ -34851,7 +35003,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="C486">
         <v>665</v>
@@ -34919,7 +35071,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="C487">
         <v>772</v>
@@ -34987,7 +35139,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="C488">
         <v>861</v>
@@ -35055,7 +35207,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="C489">
         <v>440</v>
@@ -35123,7 +35275,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="C490">
         <v>360</v>
@@ -35191,7 +35343,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="C491">
         <v>1091</v>
@@ -35259,7 +35411,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="C492">
         <v>1087</v>
@@ -35327,7 +35479,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="C493">
         <v>840</v>
@@ -35395,7 +35547,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="C494">
         <v>436</v>
@@ -35463,7 +35615,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="C495">
         <v>705</v>
@@ -35531,7 +35683,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="C496">
         <v>507</v>
@@ -35599,7 +35751,7 @@
         <v>495</v>
       </c>
       <c r="B497" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="C497">
         <v>914</v>
@@ -35667,7 +35819,7 @@
         <v>496</v>
       </c>
       <c r="B498" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="C498">
         <v>891</v>
@@ -35735,7 +35887,7 @@
         <v>497</v>
       </c>
       <c r="B499" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="C499">
         <v>399</v>
@@ -35803,7 +35955,7 @@
         <v>498</v>
       </c>
       <c r="B500" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="C500">
         <v>337</v>
@@ -35871,7 +36023,7 @@
         <v>499</v>
       </c>
       <c r="B501" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="C501">
         <v>388</v>
@@ -35939,7 +36091,7 @@
         <v>500</v>
       </c>
       <c r="B502" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="C502">
         <v>576</v>
@@ -36007,7 +36159,7 @@
         <v>501</v>
       </c>
       <c r="B503" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="C503">
         <v>917</v>
@@ -36075,7 +36227,7 @@
         <v>502</v>
       </c>
       <c r="B504" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="C504">
         <v>526</v>
@@ -36143,7 +36295,7 @@
         <v>503</v>
       </c>
       <c r="B505" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="C505">
         <v>584</v>
@@ -36211,7 +36363,7 @@
         <v>504</v>
       </c>
       <c r="B506" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="C506">
         <v>635</v>
@@ -36279,7 +36431,7 @@
         <v>505</v>
       </c>
       <c r="B507" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="C507">
         <v>861</v>
@@ -36347,7 +36499,7 @@
         <v>506</v>
       </c>
       <c r="B508" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="C508">
         <v>724</v>
@@ -36415,7 +36567,7 @@
         <v>507</v>
       </c>
       <c r="B509" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="C509">
         <v>383</v>
@@ -36483,7 +36635,7 @@
         <v>508</v>
       </c>
       <c r="B510" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="C510">
         <v>713</v>
@@ -36551,7 +36703,7 @@
         <v>509</v>
       </c>
       <c r="B511" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C511">
         <v>551</v>
@@ -36619,7 +36771,7 @@
         <v>510</v>
       </c>
       <c r="B512" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="C512">
         <v>777</v>
